--- a/output/yearly_benthic_cover_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_70_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.70948937494722</v>
+        <v>45.35830014382198</v>
       </c>
       <c r="M2" t="n">
-        <v>99.04158859917044</v>
+        <v>99.92630642770052</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.00164070611561</v>
+        <v>88.03699344094554</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91703620495402</v>
+        <v>45.93420874490131</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228673589012951</v>
+        <v>2.22875126591303</v>
       </c>
       <c r="E3" t="n">
-        <v>5.698287682055474</v>
+        <v>5.710025451353387</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428911963376506</v>
+        <v>0.7429170886376767</v>
       </c>
       <c r="G3" t="n">
-        <v>33.9693499808158</v>
+        <v>33.97494198114265</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17299503153192</v>
+        <v>34.17418607733313</v>
       </c>
       <c r="I3" t="n">
-        <v>6.546373249251502</v>
+        <v>6.562939772580193</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643069977110316</v>
+        <v>4.643231803985479</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99835929388439</v>
+        <v>11.96300655905446</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84961725918864</v>
+        <v>48.86721099617183</v>
       </c>
       <c r="M3" t="n">
-        <v>106.765012758027</v>
+        <v>106.7644263001276</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.09321555060527</v>
+        <v>87.13825885095703</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63999579955201</v>
+        <v>42.66942060991661</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184911849805312</v>
+        <v>2.185533687545184</v>
       </c>
       <c r="E4" t="n">
-        <v>6.497518226396401</v>
+        <v>6.512733120804421</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444455393652828</v>
+        <v>0.744474620490863</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30233537524861</v>
+        <v>33.31613597615245</v>
       </c>
       <c r="H4" t="n">
-        <v>34.244494810803</v>
+        <v>34.24583254257969</v>
       </c>
       <c r="I4" t="n">
-        <v>5.466725127953644</v>
+        <v>5.480582525316542</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652784621033017</v>
+        <v>4.652966378067894</v>
       </c>
       <c r="K4" t="n">
-        <v>12.90678444939474</v>
+        <v>12.86174114904296</v>
       </c>
       <c r="L4" t="n">
-        <v>44.27137604968515</v>
+        <v>44.28653435846876</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81815629863189</v>
+        <v>99.81769611742833</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.91726003804015</v>
+        <v>86.04391792573273</v>
       </c>
       <c r="C5" t="n">
-        <v>42.31252285713296</v>
+        <v>42.42572849717369</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127474614953012</v>
+        <v>2.132380362259342</v>
       </c>
       <c r="E5" t="n">
-        <v>7.087322371284718</v>
+        <v>7.116881225797981</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457636307404673</v>
+        <v>0.745794161897971</v>
       </c>
       <c r="G5" t="n">
-        <v>32.42687943488715</v>
+        <v>32.50587007958928</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30512701406149</v>
+        <v>34.30653144730666</v>
       </c>
       <c r="I5" t="n">
-        <v>4.563670279985405</v>
+        <v>4.575247137019183</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66102269212792</v>
+        <v>4.661213511862319</v>
       </c>
       <c r="K5" t="n">
-        <v>14.08273996195983</v>
+        <v>13.95608207426726</v>
       </c>
       <c r="L5" t="n">
-        <v>43.45288370513073</v>
+        <v>43.46595102507803</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84814652422352</v>
+        <v>99.84776159651898</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.61516419780229</v>
+        <v>84.77723579910024</v>
       </c>
       <c r="C6" t="n">
-        <v>41.71918730606991</v>
+        <v>41.86969469416473</v>
       </c>
       <c r="D6" t="n">
-        <v>2.064042800267855</v>
+        <v>2.070796897987563</v>
       </c>
       <c r="E6" t="n">
-        <v>7.51080412299003</v>
+        <v>7.547749660827009</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468825941772617</v>
+        <v>0.7469138661491206</v>
       </c>
       <c r="G6" t="n">
-        <v>31.46005435849151</v>
+        <v>31.56709568262922</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35659933215403</v>
+        <v>34.35803784285955</v>
       </c>
       <c r="I6" t="n">
-        <v>3.808764776113724</v>
+        <v>3.818430185215772</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668016213607885</v>
+        <v>4.668211663432004</v>
       </c>
       <c r="K6" t="n">
-        <v>15.38483580219768</v>
+        <v>15.22276420089976</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76920827284392</v>
+        <v>42.78045090668497</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87323138111152</v>
+        <v>99.87290980174946</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.03074631470093</v>
+        <v>83.33148336400377</v>
       </c>
       <c r="C7" t="n">
-        <v>40.72636110061885</v>
+        <v>41.01714119822086</v>
       </c>
       <c r="D7" t="n">
-        <v>1.986878783162391</v>
+        <v>2.000651575100489</v>
       </c>
       <c r="E7" t="n">
-        <v>7.759683543533062</v>
+        <v>7.823093711396492</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478354973778373</v>
+        <v>0.7478657783687594</v>
       </c>
       <c r="G7" t="n">
-        <v>30.28392362499005</v>
+        <v>30.49780485965326</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40043287938051</v>
+        <v>34.40182580496293</v>
       </c>
       <c r="I7" t="n">
-        <v>3.178020127645596</v>
+        <v>3.186080519717101</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673971858611482</v>
+        <v>4.674161114804747</v>
       </c>
       <c r="K7" t="n">
-        <v>16.96925368529907</v>
+        <v>16.66851663599623</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19858619252336</v>
+        <v>42.20827466063803</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89420097844126</v>
+        <v>99.89393249485511</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.01969599261254</v>
+        <v>88.17767777839273</v>
       </c>
       <c r="C8" t="n">
-        <v>43.05097249597127</v>
+        <v>43.31421884865587</v>
       </c>
       <c r="D8" t="n">
-        <v>1.991180111606953</v>
+        <v>2.004896406939578</v>
       </c>
       <c r="E8" t="n">
-        <v>9.612447818326432</v>
+        <v>9.651217274204614</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494544618179347</v>
+        <v>0.7494525436540765</v>
       </c>
       <c r="G8" t="n">
-        <v>30.79108973679553</v>
+        <v>31.00055347133265</v>
       </c>
       <c r="H8" t="n">
-        <v>34.474905243625</v>
+        <v>34.47481700808752</v>
       </c>
       <c r="I8" t="n">
-        <v>5.716528234078604</v>
+        <v>5.61266267633631</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684090386362091</v>
+        <v>4.684078397837979</v>
       </c>
       <c r="K8" t="n">
-        <v>11.98030400738747</v>
+        <v>11.82232222160727</v>
       </c>
       <c r="L8" t="n">
-        <v>44.77858418184612</v>
+        <v>44.67676628425401</v>
       </c>
       <c r="M8" t="n">
-        <v>99.80986068520485</v>
+        <v>99.81330735451715</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.05586893950661</v>
+        <v>86.10811661360708</v>
       </c>
       <c r="C9" t="n">
-        <v>41.97430733017406</v>
+        <v>42.11609501416979</v>
       </c>
       <c r="D9" t="n">
-        <v>1.902454233184111</v>
+        <v>1.911085639020089</v>
       </c>
       <c r="E9" t="n">
-        <v>9.979552491443037</v>
+        <v>9.980579273951037</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508399305175686</v>
+        <v>0.7508119632770648</v>
       </c>
       <c r="G9" t="n">
-        <v>29.41905590190104</v>
+        <v>29.55001182887733</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53863680380815</v>
+        <v>34.53735031074498</v>
       </c>
       <c r="I9" t="n">
-        <v>4.772580012917897</v>
+        <v>4.685702827254933</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692749565734803</v>
+        <v>4.692574770481656</v>
       </c>
       <c r="K9" t="n">
-        <v>13.9441310604934</v>
+        <v>13.89188338639288</v>
       </c>
       <c r="L9" t="n">
-        <v>43.92276915838593</v>
+        <v>43.83611430287242</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84120754905338</v>
+        <v>99.84409270343511</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.9040887160638</v>
+        <v>83.90192715543701</v>
       </c>
       <c r="C10" t="n">
-        <v>40.56298066873043</v>
+        <v>40.63709130629638</v>
       </c>
       <c r="D10" t="n">
-        <v>1.806190454323077</v>
+        <v>1.812158297938541</v>
       </c>
       <c r="E10" t="n">
-        <v>10.13849659571588</v>
+        <v>10.11573783667813</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520281637591815</v>
+        <v>0.7519785196744944</v>
       </c>
       <c r="G10" t="n">
-        <v>27.93045794130719</v>
+        <v>28.02035557513768</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59329553292235</v>
+        <v>34.59101190502673</v>
       </c>
       <c r="I10" t="n">
-        <v>3.983444004541211</v>
+        <v>3.910819273015829</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700176023494883</v>
+        <v>4.699865747965591</v>
       </c>
       <c r="K10" t="n">
-        <v>16.09591128393622</v>
+        <v>16.098072844563</v>
       </c>
       <c r="L10" t="n">
-        <v>43.20853638030787</v>
+        <v>43.13467743727241</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86742833297451</v>
+        <v>99.86984158813178</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.62728459906816</v>
+        <v>81.6177584440197</v>
       </c>
       <c r="C11" t="n">
-        <v>38.90362514985154</v>
+        <v>38.95923086148594</v>
       </c>
       <c r="D11" t="n">
-        <v>1.705371743925594</v>
+        <v>1.71081948113115</v>
       </c>
       <c r="E11" t="n">
-        <v>10.12658876677604</v>
+        <v>10.09394271988504</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530489718091877</v>
+        <v>0.7529807428758025</v>
       </c>
       <c r="G11" t="n">
-        <v>26.37142370783867</v>
+        <v>26.45341206709147</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64025270322264</v>
+        <v>34.63711417228691</v>
       </c>
       <c r="I11" t="n">
-        <v>3.324042631688615</v>
+        <v>3.263359617775557</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706556073807422</v>
+        <v>4.706129642973766</v>
       </c>
       <c r="K11" t="n">
-        <v>18.37271540093184</v>
+        <v>18.38224155598032</v>
       </c>
       <c r="L11" t="n">
-        <v>42.61300822686824</v>
+        <v>42.54989371383885</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88934877765162</v>
+        <v>99.89136613130511</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.17160678426563</v>
+        <v>79.13002187781468</v>
       </c>
       <c r="C12" t="n">
-        <v>36.9624279632815</v>
+        <v>36.97666283613619</v>
       </c>
       <c r="D12" t="n">
-        <v>1.597615274414289</v>
+        <v>1.60140802167413</v>
       </c>
       <c r="E12" t="n">
-        <v>9.948936724397225</v>
+        <v>9.902172425637865</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539282466369412</v>
+        <v>0.7538443233561556</v>
       </c>
       <c r="G12" t="n">
-        <v>24.70510577753092</v>
+        <v>24.76164595511993</v>
       </c>
       <c r="H12" t="n">
-        <v>34.6806993452993</v>
+        <v>34.67683887438314</v>
       </c>
       <c r="I12" t="n">
-        <v>2.773269874506084</v>
+        <v>2.722585256667473</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712051541480882</v>
+        <v>4.711527020975973</v>
       </c>
       <c r="K12" t="n">
-        <v>20.82839321573437</v>
+        <v>20.86997812218531</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11684430343723</v>
+        <v>42.06271016340697</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9076654824531</v>
+        <v>99.90935112172848</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.8022542969907</v>
+        <v>76.63601407601779</v>
       </c>
       <c r="C13" t="n">
-        <v>35.02140990716363</v>
+        <v>34.903199765195</v>
       </c>
       <c r="D13" t="n">
-        <v>1.494696833837893</v>
+        <v>1.492750167705664</v>
       </c>
       <c r="E13" t="n">
-        <v>9.693588922704015</v>
+        <v>9.608806052705496</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546852215927097</v>
+        <v>0.7545889808048736</v>
       </c>
       <c r="G13" t="n">
-        <v>23.11360186440605</v>
+        <v>23.08153240891854</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71552019326464</v>
+        <v>34.71109311702417</v>
       </c>
       <c r="I13" t="n">
-        <v>2.313378626230949</v>
+        <v>2.271062218828592</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716782634954435</v>
+        <v>4.716181130030461</v>
       </c>
       <c r="K13" t="n">
-        <v>23.19774570300929</v>
+        <v>23.3639859239822</v>
       </c>
       <c r="L13" t="n">
-        <v>41.70380911553525</v>
+        <v>41.65718694258201</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92296472570817</v>
+        <v>99.92437263175921</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.55633463744257</v>
+        <v>83.355311977521</v>
       </c>
       <c r="C14" t="n">
-        <v>39.13367778990661</v>
+        <v>39.17259343791572</v>
       </c>
       <c r="D14" t="n">
-        <v>1.496551879874988</v>
+        <v>1.494409617284468</v>
       </c>
       <c r="E14" t="n">
-        <v>12.00595329706627</v>
+        <v>11.97095929142861</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556218502105514</v>
+        <v>0.7554278367591094</v>
       </c>
       <c r="G14" t="n">
-        <v>24.92411898893799</v>
+        <v>24.99534379435483</v>
       </c>
       <c r="H14" t="n">
-        <v>36.54043628629068</v>
+        <v>36.63783276737461</v>
       </c>
       <c r="I14" t="n">
-        <v>3.111015771246137</v>
+        <v>2.779914690574926</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722636563815946</v>
+        <v>4.721423979744435</v>
       </c>
       <c r="K14" t="n">
-        <v>16.44366536255744</v>
+        <v>16.64468802247902</v>
       </c>
       <c r="L14" t="n">
-        <v>44.31908486347861</v>
+        <v>44.09015761403824</v>
       </c>
       <c r="M14" t="n">
-        <v>99.89642801594266</v>
+        <v>99.90743907443297</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.85427703665862</v>
+        <v>82.44897231443737</v>
       </c>
       <c r="C15" t="n">
-        <v>38.91227393909006</v>
+        <v>38.69590013932326</v>
       </c>
       <c r="D15" t="n">
-        <v>1.47074374067523</v>
+        <v>1.460561279600545</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23144647393159</v>
+        <v>12.08627859853732</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7564107875183412</v>
+        <v>0.7561360167406868</v>
       </c>
       <c r="G15" t="n">
-        <v>24.49430085770717</v>
+        <v>24.4291999289169</v>
       </c>
       <c r="H15" t="n">
-        <v>36.5785877947749</v>
+        <v>36.67217910526646</v>
       </c>
       <c r="I15" t="n">
-        <v>2.595219960061766</v>
+        <v>2.318767280746154</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727567421989631</v>
+        <v>4.725850104629293</v>
       </c>
       <c r="K15" t="n">
-        <v>17.14572296334138</v>
+        <v>17.55102768556263</v>
       </c>
       <c r="L15" t="n">
-        <v>43.85558599281174</v>
+        <v>43.67585232259815</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91358289524317</v>
+        <v>99.92278014748405</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.44552959185795</v>
+        <v>79.78701250175736</v>
       </c>
       <c r="C16" t="n">
-        <v>36.9046016317069</v>
+        <v>36.39226702233018</v>
       </c>
       <c r="D16" t="n">
-        <v>1.379231653671345</v>
+        <v>1.359279424446173</v>
       </c>
       <c r="E16" t="n">
-        <v>11.83115633243144</v>
+        <v>11.57047315985843</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570892359274681</v>
+        <v>0.7567469209555101</v>
       </c>
       <c r="G16" t="n">
-        <v>22.9702252970247</v>
+        <v>22.73516988492281</v>
       </c>
       <c r="H16" t="n">
-        <v>36.61139627015227</v>
+        <v>36.70180762220807</v>
       </c>
       <c r="I16" t="n">
-        <v>2.164623078104055</v>
+        <v>1.933867233394427</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731807724546674</v>
+        <v>4.729668255971939</v>
       </c>
       <c r="K16" t="n">
-        <v>19.55447040814205</v>
+        <v>20.21298749824264</v>
       </c>
       <c r="L16" t="n">
-        <v>43.468838516816</v>
+        <v>43.33033527718421</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92791055666495</v>
+        <v>99.93558979775703</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.25643195468048</v>
+        <v>81.39889496997499</v>
       </c>
       <c r="C17" t="n">
-        <v>38.20684663199872</v>
+        <v>37.57969139307336</v>
       </c>
       <c r="D17" t="n">
-        <v>1.380451643593748</v>
+        <v>1.360340031856698</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65865327385317</v>
+        <v>12.31774721807962</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577589140310214</v>
+        <v>0.7573373892417383</v>
       </c>
       <c r="G17" t="n">
-        <v>23.44377840529373</v>
+        <v>23.17358912754413</v>
       </c>
       <c r="H17" t="n">
-        <v>37.09701558287122</v>
+        <v>37.15112463847172</v>
       </c>
       <c r="I17" t="n">
-        <v>2.182780922343694</v>
+        <v>1.905397882020206</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735993212693882</v>
+        <v>4.733358682760866</v>
       </c>
       <c r="K17" t="n">
-        <v>17.74356804531952</v>
+        <v>18.60110503002502</v>
       </c>
       <c r="L17" t="n">
-        <v>43.97689026052349</v>
+        <v>43.75573983313754</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92730493784173</v>
+        <v>99.93653625623593</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.93307692519519</v>
+        <v>78.89247344607877</v>
       </c>
       <c r="C18" t="n">
-        <v>36.22045122427857</v>
+        <v>35.36723083755103</v>
       </c>
       <c r="D18" t="n">
-        <v>1.295868113790769</v>
+        <v>1.26866930502985</v>
       </c>
       <c r="E18" t="n">
-        <v>12.186421870769</v>
+        <v>11.75249392220168</v>
       </c>
       <c r="F18" t="n">
-        <v>0.758334144296766</v>
+        <v>0.7578458160739154</v>
       </c>
       <c r="G18" t="n">
-        <v>22.00732277959986</v>
+        <v>21.61196504182988</v>
       </c>
       <c r="H18" t="n">
-        <v>37.12517668495388</v>
+        <v>37.17606547577894</v>
       </c>
       <c r="I18" t="n">
-        <v>1.820364929930127</v>
+        <v>1.588897534702546</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739588401854786</v>
+        <v>4.736536350461972</v>
       </c>
       <c r="K18" t="n">
-        <v>20.0669230748048</v>
+        <v>21.10752655392121</v>
       </c>
       <c r="L18" t="n">
-        <v>43.65199289751818</v>
+        <v>43.47231488958275</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93936719660155</v>
+        <v>99.947072281055</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.03372730576582</v>
+        <v>77.85573805291712</v>
       </c>
       <c r="C19" t="n">
-        <v>35.60142575151733</v>
+        <v>34.56638888111536</v>
       </c>
       <c r="D19" t="n">
-        <v>1.263837853899691</v>
+        <v>1.231031306096882</v>
       </c>
       <c r="E19" t="n">
-        <v>12.13819770105383</v>
+        <v>11.62601186619286</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7588196362721196</v>
+        <v>0.7582783603708525</v>
       </c>
       <c r="G19" t="n">
-        <v>21.46336289615509</v>
+        <v>20.97079628811387</v>
       </c>
       <c r="H19" t="n">
-        <v>37.14894453913752</v>
+        <v>37.19728390143102</v>
       </c>
       <c r="I19" t="n">
-        <v>1.517941952546815</v>
+        <v>1.333096578393798</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742622726700746</v>
+        <v>4.739239752317829</v>
       </c>
       <c r="K19" t="n">
-        <v>20.96627269423418</v>
+        <v>22.14426194708288</v>
       </c>
       <c r="L19" t="n">
-        <v>43.38173586175044</v>
+        <v>43.24493796710625</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94943430750195</v>
+        <v>99.95558879530448</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.59078558842621</v>
+        <v>75.15766955967489</v>
       </c>
       <c r="C20" t="n">
-        <v>33.3921016412282</v>
+        <v>32.07320163008696</v>
       </c>
       <c r="D20" t="n">
-        <v>1.175930895674604</v>
+        <v>1.13340413650582</v>
       </c>
       <c r="E20" t="n">
-        <v>11.50485987992895</v>
+        <v>10.88925237816504</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592376146876226</v>
+        <v>0.7586521510789285</v>
       </c>
       <c r="G20" t="n">
-        <v>19.97046652526356</v>
+        <v>19.30770333869851</v>
       </c>
       <c r="H20" t="n">
-        <v>37.16940718432204</v>
+        <v>37.21562017451313</v>
       </c>
       <c r="I20" t="n">
-        <v>1.265648396751806</v>
+        <v>1.111461436470142</v>
       </c>
       <c r="J20" t="n">
-        <v>4.74523509179764</v>
+        <v>4.741575944243303</v>
       </c>
       <c r="K20" t="n">
-        <v>23.40921441157377</v>
+        <v>24.8423304403251</v>
       </c>
       <c r="L20" t="n">
-        <v>43.15651889296061</v>
+        <v>43.04743746907702</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95783494576258</v>
+        <v>99.96296953948908</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.33747522766605</v>
+        <v>81.30013115092775</v>
       </c>
       <c r="C21" t="n">
-        <v>36.8870381879521</v>
+        <v>35.97699680196115</v>
       </c>
       <c r="D21" t="n">
-        <v>1.176832356132831</v>
+        <v>1.134100119041923</v>
       </c>
       <c r="E21" t="n">
-        <v>13.41108195054616</v>
+        <v>12.96593389288836</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7598196409704225</v>
+        <v>0.7591180119586638</v>
       </c>
       <c r="G21" t="n">
-        <v>21.56758158761096</v>
+        <v>21.13993695214245</v>
       </c>
       <c r="H21" t="n">
-        <v>38.77970683513851</v>
+        <v>39.05885039276402</v>
       </c>
       <c r="I21" t="n">
-        <v>1.893580101202033</v>
+        <v>1.497704207390682</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748872756065139</v>
+        <v>4.744487574741649</v>
       </c>
       <c r="K21" t="n">
-        <v>17.66252477233394</v>
+        <v>18.69986884907225</v>
       </c>
       <c r="L21" t="n">
-        <v>45.38736605278779</v>
+        <v>45.27324151277522</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93692901307384</v>
+        <v>99.95010716380862</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_70_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.35830014382198</v>
+        <v>45.20448580044252</v>
       </c>
       <c r="M2" t="n">
-        <v>99.92630642770052</v>
+        <v>100.6424702833584</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.03699344094554</v>
+        <v>88.01511028461788</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93420874490131</v>
+        <v>45.91419602248101</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22875126591303</v>
+        <v>2.228710308384523</v>
       </c>
       <c r="E3" t="n">
-        <v>5.710025451353387</v>
+        <v>5.697437534747672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429170886376767</v>
+        <v>0.7429034361281746</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97494198114265</v>
+        <v>33.96821621094426</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17418607733313</v>
+        <v>34.17355806189602</v>
       </c>
       <c r="I3" t="n">
-        <v>6.562939772580193</v>
+        <v>6.561138256716138</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643231803985479</v>
+        <v>4.643146475801091</v>
       </c>
       <c r="K3" t="n">
-        <v>11.96300655905446</v>
+        <v>11.98488971538212</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86721099617183</v>
+        <v>48.86540089884213</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7644263001276</v>
+        <v>106.7644866367053</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13825885095703</v>
+        <v>87.10505056292509</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66942060991661</v>
+        <v>42.63847697083352</v>
       </c>
       <c r="D4" t="n">
-        <v>2.185533687545184</v>
+        <v>2.184868147256243</v>
       </c>
       <c r="E4" t="n">
-        <v>6.512733120804421</v>
+        <v>6.498540061619246</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744474620490863</v>
+        <v>0.7444611058009626</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31613597615245</v>
+        <v>33.30000913048258</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24583254257969</v>
+        <v>34.24521086684427</v>
       </c>
       <c r="I4" t="n">
-        <v>5.480582525316542</v>
+        <v>5.479079339665756</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652966378067894</v>
+        <v>4.652881911256016</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86174114904296</v>
+        <v>12.89494943707492</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28653435846876</v>
+        <v>44.28431975162723</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81769611742833</v>
+        <v>99.81774615953567</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.04391792573273</v>
+        <v>85.88718530623748</v>
       </c>
       <c r="C5" t="n">
-        <v>42.42572849717369</v>
+        <v>42.27099643009169</v>
       </c>
       <c r="D5" t="n">
-        <v>2.132380362259342</v>
+        <v>2.125255021352122</v>
       </c>
       <c r="E5" t="n">
-        <v>7.116881225797981</v>
+        <v>7.083564512972365</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745794161897971</v>
+        <v>0.7457826722569005</v>
       </c>
       <c r="G5" t="n">
-        <v>32.50587007958928</v>
+        <v>32.39143364532265</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30653144730666</v>
+        <v>34.30600292381742</v>
       </c>
       <c r="I5" t="n">
-        <v>4.575247137019183</v>
+        <v>4.574004828910408</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661213511862319</v>
+        <v>4.661141701605628</v>
       </c>
       <c r="K5" t="n">
-        <v>13.95608207426726</v>
+        <v>14.1128146937625</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46595102507803</v>
+        <v>43.46399222782176</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84776159651898</v>
+        <v>99.84780335167595</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.77723579910024</v>
+        <v>84.40129508021907</v>
       </c>
       <c r="C6" t="n">
-        <v>41.86969469416473</v>
+        <v>41.49542407434537</v>
       </c>
       <c r="D6" t="n">
-        <v>2.070796897987563</v>
+        <v>2.052434215233026</v>
       </c>
       <c r="E6" t="n">
-        <v>7.547749660827009</v>
+        <v>7.477085921829573</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469138661491206</v>
+        <v>0.7469070482520943</v>
       </c>
       <c r="G6" t="n">
-        <v>31.56709568262922</v>
+        <v>31.28155728427073</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35803784285955</v>
+        <v>34.35772421959634</v>
       </c>
       <c r="I6" t="n">
-        <v>3.818430185215772</v>
+        <v>3.817417339461711</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668211663432004</v>
+        <v>4.668169051575589</v>
       </c>
       <c r="K6" t="n">
-        <v>15.22276420089976</v>
+        <v>15.59870491978094</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78045090668497</v>
+        <v>42.77881531618173</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87290980174946</v>
+        <v>99.87294431030804</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.33148336400377</v>
+        <v>82.82166342237821</v>
       </c>
       <c r="C7" t="n">
-        <v>41.01714119822086</v>
+        <v>40.50854966444759</v>
       </c>
       <c r="D7" t="n">
-        <v>2.000651575100489</v>
+        <v>1.975522119929374</v>
       </c>
       <c r="E7" t="n">
-        <v>7.823093711396492</v>
+        <v>7.727769159462678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478657783687594</v>
+        <v>0.7478645644910984</v>
       </c>
       <c r="G7" t="n">
-        <v>30.49780485965326</v>
+        <v>30.10932477263268</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40182580496293</v>
+        <v>34.40176996659052</v>
       </c>
       <c r="I7" t="n">
-        <v>3.186080519717101</v>
+        <v>3.185259311202488</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674161114804747</v>
+        <v>4.674153528069365</v>
       </c>
       <c r="K7" t="n">
-        <v>16.66851663599623</v>
+        <v>17.17833657762179</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20827466063803</v>
+        <v>42.20707438739002</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89393249485511</v>
+        <v>99.8939606294594</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.17767777839273</v>
+        <v>87.82048464474994</v>
       </c>
       <c r="C8" t="n">
-        <v>43.31421884865587</v>
+        <v>42.87136081636926</v>
       </c>
       <c r="D8" t="n">
-        <v>2.004896406939578</v>
+        <v>1.979793194150109</v>
       </c>
       <c r="E8" t="n">
-        <v>9.651217274204614</v>
+        <v>9.60484026202025</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494525436540765</v>
+        <v>0.7494814459371608</v>
       </c>
       <c r="G8" t="n">
-        <v>31.00055347133265</v>
+        <v>30.62993369646547</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47481700808752</v>
+        <v>34.47614651310939</v>
       </c>
       <c r="I8" t="n">
-        <v>5.61266267633631</v>
+        <v>5.696030495960298</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684078397837979</v>
+        <v>4.684259037107255</v>
       </c>
       <c r="K8" t="n">
-        <v>11.82232222160727</v>
+        <v>12.17951535525006</v>
       </c>
       <c r="L8" t="n">
-        <v>44.67676628425401</v>
+        <v>44.75966575309937</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81330735451715</v>
+        <v>99.81054192471869</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.10811661360708</v>
+        <v>85.85156294728617</v>
       </c>
       <c r="C9" t="n">
-        <v>42.11609501416979</v>
+        <v>41.78624224777033</v>
       </c>
       <c r="D9" t="n">
-        <v>1.911085639020089</v>
+        <v>1.890939002243732</v>
       </c>
       <c r="E9" t="n">
-        <v>9.980579273951037</v>
+        <v>9.966345875515849</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508119632770648</v>
+        <v>0.7508652787408845</v>
       </c>
       <c r="G9" t="n">
-        <v>29.55001182887733</v>
+        <v>29.25524566602515</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53735031074498</v>
+        <v>34.53980282208068</v>
       </c>
       <c r="I9" t="n">
-        <v>4.685702827254933</v>
+        <v>4.755456310549328</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692574770481656</v>
+        <v>4.692907992130528</v>
       </c>
       <c r="K9" t="n">
-        <v>13.89188338639288</v>
+        <v>14.14843705271386</v>
       </c>
       <c r="L9" t="n">
-        <v>43.83611430287242</v>
+        <v>43.90709763018356</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84409270343511</v>
+        <v>99.84177693066775</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.90192715543701</v>
+        <v>83.7710601105268</v>
       </c>
       <c r="C10" t="n">
-        <v>40.63709130629638</v>
+        <v>40.44337302889814</v>
       </c>
       <c r="D10" t="n">
-        <v>1.812158297938541</v>
+        <v>1.798083227687135</v>
       </c>
       <c r="E10" t="n">
-        <v>10.11573783667813</v>
+        <v>10.13846523701636</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519785196744944</v>
+        <v>0.7520511650966378</v>
       </c>
       <c r="G10" t="n">
-        <v>28.02035557513768</v>
+        <v>27.81864803228924</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59101190502673</v>
+        <v>34.59435359444533</v>
       </c>
       <c r="I10" t="n">
-        <v>3.910819273015829</v>
+        <v>3.96913907213811</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699865747965591</v>
+        <v>4.700319781853986</v>
       </c>
       <c r="K10" t="n">
-        <v>16.098072844563</v>
+        <v>16.22893988947319</v>
       </c>
       <c r="L10" t="n">
-        <v>43.13467743727241</v>
+        <v>43.19559107300232</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86984158813178</v>
+        <v>99.86790399137365</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.6177584440197</v>
+        <v>81.6315604493515</v>
       </c>
       <c r="C11" t="n">
-        <v>38.95923086148594</v>
+        <v>38.91901731648878</v>
       </c>
       <c r="D11" t="n">
-        <v>1.71081948113115</v>
+        <v>1.703616995275951</v>
       </c>
       <c r="E11" t="n">
-        <v>10.09394271988504</v>
+        <v>10.1578336885684</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529807428758025</v>
+        <v>0.7530682801268576</v>
       </c>
       <c r="G11" t="n">
-        <v>26.45341206709147</v>
+        <v>26.35713455509416</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63711417228691</v>
+        <v>34.64114088583544</v>
       </c>
       <c r="I11" t="n">
-        <v>3.263359617775557</v>
+        <v>3.312089293657821</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706129642973766</v>
+        <v>4.70667675079286</v>
       </c>
       <c r="K11" t="n">
-        <v>18.38224155598032</v>
+        <v>18.36843955064852</v>
       </c>
       <c r="L11" t="n">
-        <v>42.54989371383885</v>
+        <v>42.60228926974774</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89136613130511</v>
+        <v>99.88974613688504</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.13002187781468</v>
+        <v>79.35373444315842</v>
       </c>
       <c r="C12" t="n">
-        <v>36.97666283613619</v>
+        <v>37.15383991476922</v>
       </c>
       <c r="D12" t="n">
-        <v>1.60140802167413</v>
+        <v>1.603941101454687</v>
       </c>
       <c r="E12" t="n">
-        <v>9.902172425637865</v>
+        <v>10.02406151424598</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538443233561556</v>
+        <v>0.7539423986699553</v>
       </c>
       <c r="G12" t="n">
-        <v>24.76164595511993</v>
+        <v>24.8150209505508</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67683887438314</v>
+        <v>34.68135033881794</v>
       </c>
       <c r="I12" t="n">
-        <v>2.722585256667473</v>
+        <v>2.763278147731841</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711527020975973</v>
+        <v>4.71213999168722</v>
       </c>
       <c r="K12" t="n">
-        <v>20.86997812218531</v>
+        <v>20.64626555684159</v>
       </c>
       <c r="L12" t="n">
-        <v>42.06271016340697</v>
+        <v>42.10789204800982</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90935112172848</v>
+        <v>99.90799751962062</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.63601407601779</v>
+        <v>76.93805494741949</v>
       </c>
       <c r="C13" t="n">
-        <v>34.903199765195</v>
+        <v>35.16507510081192</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492750167705664</v>
+        <v>1.499117106476448</v>
       </c>
       <c r="E13" t="n">
-        <v>9.608806052705496</v>
+        <v>9.753120724697318</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545889808048736</v>
+        <v>0.7546953251283277</v>
       </c>
       <c r="G13" t="n">
-        <v>23.08153240891854</v>
+        <v>23.19325963453597</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71109311702417</v>
+        <v>34.71598495590307</v>
       </c>
       <c r="I13" t="n">
-        <v>2.271062218828592</v>
+        <v>2.30503141862632</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716181130030461</v>
+        <v>4.716845782052047</v>
       </c>
       <c r="K13" t="n">
-        <v>23.3639859239822</v>
+        <v>23.06194505258051</v>
       </c>
       <c r="L13" t="n">
-        <v>41.65718694258201</v>
+        <v>41.69622212028169</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92437263175921</v>
+        <v>99.92324227367412</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.355311977521</v>
+        <v>83.51980380536753</v>
       </c>
       <c r="C14" t="n">
-        <v>39.17259343791572</v>
+        <v>39.3231150620207</v>
       </c>
       <c r="D14" t="n">
-        <v>1.494409617284468</v>
+        <v>1.500821004907424</v>
       </c>
       <c r="E14" t="n">
-        <v>11.97095929142861</v>
+        <v>12.06533212023757</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554278367591094</v>
+        <v>0.7555531128053515</v>
       </c>
       <c r="G14" t="n">
-        <v>24.99534379435483</v>
+        <v>25.04610352721651</v>
       </c>
       <c r="H14" t="n">
-        <v>36.63783276737461</v>
+        <v>36.58192559300125</v>
       </c>
       <c r="I14" t="n">
-        <v>2.779914690574926</v>
+        <v>2.847861492165997</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721423979744435</v>
+        <v>4.722206955033446</v>
       </c>
       <c r="K14" t="n">
-        <v>16.64468802247902</v>
+        <v>16.48019619463246</v>
       </c>
       <c r="L14" t="n">
-        <v>44.09015761403824</v>
+        <v>44.10186780054681</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90743907443297</v>
+        <v>99.90517905719997</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.44897231443737</v>
+        <v>82.70575824396016</v>
       </c>
       <c r="C15" t="n">
-        <v>38.69590013932326</v>
+        <v>38.94710467975069</v>
       </c>
       <c r="D15" t="n">
-        <v>1.460561279600545</v>
+        <v>1.470330148533377</v>
       </c>
       <c r="E15" t="n">
-        <v>12.08627859853732</v>
+        <v>12.21832436318965</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561360167406868</v>
+        <v>0.7562764840010037</v>
       </c>
       <c r="G15" t="n">
-        <v>24.4291999289169</v>
+        <v>24.53946188150993</v>
       </c>
       <c r="H15" t="n">
-        <v>36.67217910526646</v>
+        <v>36.61914729816291</v>
       </c>
       <c r="I15" t="n">
-        <v>2.318767280746154</v>
+        <v>2.37549004355702</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725850104629293</v>
+        <v>4.726728025006271</v>
       </c>
       <c r="K15" t="n">
-        <v>17.55102768556263</v>
+        <v>17.29424175603983</v>
       </c>
       <c r="L15" t="n">
-        <v>43.67585232259815</v>
+        <v>43.67954630053819</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92278014748405</v>
+        <v>99.92089273632872</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.78701250175736</v>
+        <v>80.18164562643344</v>
       </c>
       <c r="C16" t="n">
-        <v>36.39226702233018</v>
+        <v>36.79020943242349</v>
       </c>
       <c r="D16" t="n">
-        <v>1.359279424446173</v>
+        <v>1.374378757850498</v>
       </c>
       <c r="E16" t="n">
-        <v>11.57047315985843</v>
+        <v>11.75117699652751</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567469209555101</v>
+        <v>0.7568993776409221</v>
       </c>
       <c r="G16" t="n">
-        <v>22.73516988492281</v>
+        <v>22.93805590035051</v>
       </c>
       <c r="H16" t="n">
-        <v>36.70180762220807</v>
+        <v>36.6493080058324</v>
       </c>
       <c r="I16" t="n">
-        <v>1.933867233394427</v>
+        <v>1.98120547797584</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729668255971939</v>
+        <v>4.730621110255761</v>
       </c>
       <c r="K16" t="n">
-        <v>20.21298749824264</v>
+        <v>19.81835437356656</v>
       </c>
       <c r="L16" t="n">
-        <v>43.33033527718421</v>
+        <v>43.32545035946671</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93558979775703</v>
+        <v>99.93401416545674</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.39889496997499</v>
+        <v>81.88209155505116</v>
       </c>
       <c r="C17" t="n">
-        <v>37.57969139307336</v>
+        <v>38.03976141343946</v>
       </c>
       <c r="D17" t="n">
-        <v>1.360340031856698</v>
+        <v>1.375470802678139</v>
       </c>
       <c r="E17" t="n">
-        <v>12.31774721807962</v>
+        <v>12.53327708536665</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573373892417383</v>
+        <v>0.7575007897667105</v>
       </c>
       <c r="G17" t="n">
-        <v>23.17358912754413</v>
+        <v>23.40373811888491</v>
       </c>
       <c r="H17" t="n">
-        <v>37.15112463847172</v>
+        <v>37.12588482082119</v>
       </c>
       <c r="I17" t="n">
-        <v>1.905397882020206</v>
+        <v>1.951840001491632</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733358682760866</v>
+        <v>4.734379936041939</v>
       </c>
       <c r="K17" t="n">
-        <v>18.60110503002502</v>
+        <v>18.11790844494882</v>
       </c>
       <c r="L17" t="n">
-        <v>43.75573983313754</v>
+        <v>43.77732046319105</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93653625623593</v>
+        <v>99.93499032157933</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.89247344607877</v>
+        <v>79.43463379827206</v>
       </c>
       <c r="C18" t="n">
-        <v>35.36723083755103</v>
+        <v>35.89361792901333</v>
       </c>
       <c r="D18" t="n">
-        <v>1.26866930502985</v>
+        <v>1.286126654510562</v>
       </c>
       <c r="E18" t="n">
-        <v>11.75249392220168</v>
+        <v>11.99044808921429</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578458160739154</v>
+        <v>0.7580181719067446</v>
       </c>
       <c r="G18" t="n">
-        <v>21.61196504182988</v>
+        <v>21.8835407856536</v>
       </c>
       <c r="H18" t="n">
-        <v>37.17606547577894</v>
+        <v>37.15124224618463</v>
       </c>
       <c r="I18" t="n">
-        <v>1.588897534702546</v>
+        <v>1.627644276385066</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736536350461972</v>
+        <v>4.737613574417152</v>
       </c>
       <c r="K18" t="n">
-        <v>21.10752655392121</v>
+        <v>20.56536620172795</v>
       </c>
       <c r="L18" t="n">
-        <v>43.47231488958275</v>
+        <v>43.48679809143949</v>
       </c>
       <c r="M18" t="n">
-        <v>99.947072281055</v>
+        <v>99.94578222218078</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.85573805291712</v>
+        <v>78.44357912578899</v>
       </c>
       <c r="C19" t="n">
-        <v>34.56638888111536</v>
+        <v>35.14713843747492</v>
       </c>
       <c r="D19" t="n">
-        <v>1.231031306096882</v>
+        <v>1.250343502908557</v>
       </c>
       <c r="E19" t="n">
-        <v>11.62601186619286</v>
+        <v>11.88400615357357</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582783603708525</v>
+        <v>0.7584571941956366</v>
       </c>
       <c r="G19" t="n">
-        <v>20.97079628811387</v>
+        <v>21.27468779689436</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19728390143102</v>
+        <v>37.17275917547548</v>
       </c>
       <c r="I19" t="n">
-        <v>1.333096578393798</v>
+        <v>1.362967839018645</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739239752317829</v>
+        <v>4.740357463722727</v>
       </c>
       <c r="K19" t="n">
-        <v>22.14426194708288</v>
+        <v>21.55642087421102</v>
       </c>
       <c r="L19" t="n">
-        <v>43.24493796710625</v>
+        <v>43.25103472483946</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95558879530448</v>
+        <v>99.95459403652541</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.15766955967489</v>
+        <v>75.81325122413979</v>
       </c>
       <c r="C20" t="n">
-        <v>32.07320163008696</v>
+        <v>32.72646783467553</v>
       </c>
       <c r="D20" t="n">
-        <v>1.13340413650582</v>
+        <v>1.155340535628196</v>
       </c>
       <c r="E20" t="n">
-        <v>10.88925237816504</v>
+        <v>11.17043728276897</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586521510789285</v>
+        <v>0.7588361477601819</v>
       </c>
       <c r="G20" t="n">
-        <v>19.30770333869851</v>
+        <v>19.65820523512902</v>
       </c>
       <c r="H20" t="n">
-        <v>37.21562017451313</v>
+        <v>37.19133207543785</v>
       </c>
       <c r="I20" t="n">
-        <v>1.111461436470142</v>
+        <v>1.136374023914425</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741575944243303</v>
+        <v>4.742725923501135</v>
       </c>
       <c r="K20" t="n">
-        <v>24.8423304403251</v>
+        <v>24.18674877586021</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04743746907702</v>
+        <v>43.04892317171375</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96296953948908</v>
+        <v>99.96213978224949</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.30013115092775</v>
+        <v>81.78742162393068</v>
       </c>
       <c r="C21" t="n">
-        <v>35.97699680196115</v>
+        <v>36.50147370403536</v>
       </c>
       <c r="D21" t="n">
-        <v>1.134100119041923</v>
+        <v>1.156070878627953</v>
       </c>
       <c r="E21" t="n">
-        <v>12.96593389288836</v>
+        <v>13.18726770001094</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7591180119586638</v>
+        <v>0.7593158424055167</v>
       </c>
       <c r="G21" t="n">
-        <v>21.13993695214245</v>
+        <v>21.42189351520082</v>
       </c>
       <c r="H21" t="n">
-        <v>39.05885039276402</v>
+        <v>38.96610383787418</v>
       </c>
       <c r="I21" t="n">
-        <v>1.497704207390682</v>
+        <v>1.551045834776785</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744487574741649</v>
+        <v>4.745724015034478</v>
       </c>
       <c r="K21" t="n">
-        <v>18.69986884907225</v>
+        <v>18.21257837606935</v>
       </c>
       <c r="L21" t="n">
-        <v>45.27324151277522</v>
+        <v>45.23427905429591</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95010716380862</v>
+        <v>99.94833113440062</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_70_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_70_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.20448580044252</v>
+        <v>43.23107531312685</v>
       </c>
       <c r="M2" t="n">
-        <v>100.6424702833584</v>
+        <v>98.4998697478708</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.01511028461788</v>
+        <v>81.57792216754692</v>
       </c>
       <c r="C3" t="n">
-        <v>45.91419602248101</v>
+        <v>43.33347772310249</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228710308384523</v>
+        <v>2.185438698318194</v>
       </c>
       <c r="E3" t="n">
-        <v>5.697437534747672</v>
+        <v>4.163327121242305</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429034361281746</v>
+        <v>0.7377041961239521</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96821621094426</v>
+        <v>32.87264042053618</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17355806189602</v>
+        <v>33.93439302170179</v>
       </c>
       <c r="I3" t="n">
-        <v>6.561138256716138</v>
+        <v>3.0737674838498</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643146475801091</v>
+        <v>4.6106512257747</v>
       </c>
       <c r="K3" t="n">
-        <v>11.98488971538212</v>
+        <v>18.42207783245307</v>
       </c>
       <c r="L3" t="n">
-        <v>48.86540089884213</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7644866367053</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.10505056292509</v>
+        <v>88.76083136885366</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63847697083352</v>
+        <v>42.94970750148863</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184868147256243</v>
+        <v>2.191225040058169</v>
       </c>
       <c r="E4" t="n">
-        <v>6.498540061619246</v>
+        <v>6.56504417359972</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444611058009626</v>
+        <v>0.7396574005698471</v>
       </c>
       <c r="G4" t="n">
-        <v>33.30000913048258</v>
+        <v>33.56749795716855</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24521086684427</v>
+        <v>34.02424042621296</v>
       </c>
       <c r="I4" t="n">
-        <v>5.479079339665756</v>
+        <v>7.050307617682872</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652881911256016</v>
+        <v>4.622858753561544</v>
       </c>
       <c r="K4" t="n">
-        <v>12.89494943707492</v>
+        <v>11.23916863114634</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28431975162723</v>
+        <v>45.57673420220733</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81774615953567</v>
+        <v>99.76561033484231</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.88718530623748</v>
+        <v>87.8092431987519</v>
       </c>
       <c r="C5" t="n">
-        <v>42.27099643009169</v>
+        <v>43.09104579263938</v>
       </c>
       <c r="D5" t="n">
-        <v>2.125255021352122</v>
+        <v>2.146746452402091</v>
       </c>
       <c r="E5" t="n">
-        <v>7.083564512972365</v>
+        <v>7.41318182002434</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457826722569005</v>
+        <v>0.7413107537375123</v>
       </c>
       <c r="G5" t="n">
-        <v>32.39143364532265</v>
+        <v>32.8861280052062</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30600292381742</v>
+        <v>34.10029467192556</v>
       </c>
       <c r="I5" t="n">
-        <v>4.574004828910408</v>
+        <v>5.888389284596758</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661141701605628</v>
+        <v>4.633192210859452</v>
       </c>
       <c r="K5" t="n">
-        <v>14.1128146937625</v>
+        <v>12.19075680124809</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46399222782176</v>
+        <v>44.52235552784356</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84780335167595</v>
+        <v>99.80415812173104</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.40129508021907</v>
+        <v>86.61753905278577</v>
       </c>
       <c r="C6" t="n">
-        <v>41.49542407434537</v>
+        <v>42.81349473048689</v>
       </c>
       <c r="D6" t="n">
-        <v>2.052434215233026</v>
+        <v>2.090422472936196</v>
       </c>
       <c r="E6" t="n">
-        <v>7.477085921829573</v>
+        <v>8.03806202405643</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469070482520943</v>
+        <v>0.742713274692163</v>
       </c>
       <c r="G6" t="n">
-        <v>31.28155728427073</v>
+        <v>32.02329783893043</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35772421959634</v>
+        <v>34.16481063583949</v>
       </c>
       <c r="I6" t="n">
-        <v>3.817417339461711</v>
+        <v>4.916274839505043</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668169051575589</v>
+        <v>4.641957966826019</v>
       </c>
       <c r="K6" t="n">
-        <v>15.59870491978094</v>
+        <v>13.38246094721424</v>
       </c>
       <c r="L6" t="n">
-        <v>42.77881531618173</v>
+        <v>43.64047795328231</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87294431030804</v>
+        <v>99.83643363098344</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.82166342237821</v>
+        <v>85.1273498019214</v>
       </c>
       <c r="C7" t="n">
-        <v>40.50854966444759</v>
+        <v>42.08712230968209</v>
       </c>
       <c r="D7" t="n">
-        <v>1.975522119929374</v>
+        <v>2.01976004568666</v>
       </c>
       <c r="E7" t="n">
-        <v>7.727769159462678</v>
+        <v>8.450264987286054</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478645644910984</v>
+        <v>0.7439066663300143</v>
       </c>
       <c r="G7" t="n">
-        <v>30.10932477263268</v>
+        <v>30.9408161955642</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40176996659052</v>
+        <v>34.21970665118066</v>
       </c>
       <c r="I7" t="n">
-        <v>3.185259311202488</v>
+        <v>4.103478591311214</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674153528069365</v>
+        <v>4.64941666456259</v>
       </c>
       <c r="K7" t="n">
-        <v>17.17833657762179</v>
+        <v>14.87265019807862</v>
       </c>
       <c r="L7" t="n">
-        <v>42.20707438739002</v>
+        <v>42.90366430225305</v>
       </c>
       <c r="M7" t="n">
-        <v>99.8939606294594</v>
+        <v>99.86343681001375</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.82048464474994</v>
+        <v>83.41293043737578</v>
       </c>
       <c r="C8" t="n">
-        <v>42.87136081636926</v>
+        <v>41.01025611244788</v>
       </c>
       <c r="D8" t="n">
-        <v>1.979793194150109</v>
+        <v>1.93879086415485</v>
       </c>
       <c r="E8" t="n">
-        <v>9.60484026202025</v>
+        <v>8.682213875726712</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494814459371608</v>
+        <v>0.7449246214267363</v>
       </c>
       <c r="G8" t="n">
-        <v>30.62993369646547</v>
+        <v>29.70044481153215</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47614651310939</v>
+        <v>34.26653258562987</v>
       </c>
       <c r="I8" t="n">
-        <v>5.696030495960298</v>
+        <v>3.424244794988349</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684259037107255</v>
+        <v>4.655778883917103</v>
       </c>
       <c r="K8" t="n">
-        <v>12.17951535525006</v>
+        <v>16.58706956262423</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75966575309937</v>
+        <v>42.2886888085026</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81054192471869</v>
+        <v>99.8860144835747</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.85156294728617</v>
+        <v>81.48358984550897</v>
       </c>
       <c r="C9" t="n">
-        <v>41.78624224777033</v>
+        <v>39.61262313583314</v>
       </c>
       <c r="D9" t="n">
-        <v>1.890939002243732</v>
+        <v>1.848179109104443</v>
       </c>
       <c r="E9" t="n">
-        <v>9.966345875515849</v>
+        <v>8.752585395533158</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508652787408845</v>
+        <v>0.745795207544616</v>
       </c>
       <c r="G9" t="n">
-        <v>29.25524566602515</v>
+        <v>28.3123583088016</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53980282208068</v>
+        <v>34.30657954705234</v>
       </c>
       <c r="I9" t="n">
-        <v>4.755456310549328</v>
+        <v>2.856872230318981</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692907992130528</v>
+        <v>4.661220047153851</v>
       </c>
       <c r="K9" t="n">
-        <v>14.14843705271386</v>
+        <v>18.51641015449103</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90709763018356</v>
+        <v>41.77584879870393</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84177693066775</v>
+        <v>99.90488208902809</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.7710601105268</v>
+        <v>86.17968231291457</v>
       </c>
       <c r="C10" t="n">
-        <v>40.44337302889814</v>
+        <v>42.88298039291399</v>
       </c>
       <c r="D10" t="n">
-        <v>1.798083227687135</v>
+        <v>1.850225761155926</v>
       </c>
       <c r="E10" t="n">
-        <v>10.13846523701636</v>
+        <v>10.61468018221602</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520511650966378</v>
+        <v>0.7466210924840074</v>
       </c>
       <c r="G10" t="n">
-        <v>27.81864803228924</v>
+        <v>29.71894147082498</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59435359444533</v>
+        <v>35.71980063996342</v>
       </c>
       <c r="I10" t="n">
-        <v>3.96913907213811</v>
+        <v>2.863031338245147</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700319781853986</v>
+        <v>4.666381828025047</v>
       </c>
       <c r="K10" t="n">
-        <v>16.22893988947319</v>
+        <v>13.82031768708545</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19559107300232</v>
+        <v>43.20137310807674</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86790399137365</v>
+        <v>99.90467118807616</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.6315604493515</v>
+        <v>85.85054157758876</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91901731648878</v>
+        <v>42.87247527545514</v>
       </c>
       <c r="D11" t="n">
-        <v>1.703616995275951</v>
+        <v>1.82694080651956</v>
       </c>
       <c r="E11" t="n">
-        <v>10.1578336885684</v>
+        <v>10.942733374009</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530682801268576</v>
+        <v>0.7473344679129187</v>
       </c>
       <c r="G11" t="n">
-        <v>26.35713455509416</v>
+        <v>29.3964300698443</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64114088583544</v>
+        <v>35.80542918743271</v>
       </c>
       <c r="I11" t="n">
-        <v>3.312089293657821</v>
+        <v>2.460833247414515</v>
       </c>
       <c r="J11" t="n">
-        <v>4.70667675079286</v>
+        <v>4.670840424455743</v>
       </c>
       <c r="K11" t="n">
-        <v>18.36843955064852</v>
+        <v>14.14945842241124</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60228926974774</v>
+        <v>42.89611682763498</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88974613688504</v>
+        <v>99.91805052550137</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.35373444315842</v>
+        <v>83.87680654053986</v>
       </c>
       <c r="C12" t="n">
-        <v>37.15383991476922</v>
+        <v>41.2814860767111</v>
       </c>
       <c r="D12" t="n">
-        <v>1.603941101454687</v>
+        <v>1.742844673741369</v>
       </c>
       <c r="E12" t="n">
-        <v>10.02406151424598</v>
+        <v>10.78108825587806</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539423986699553</v>
+        <v>0.7479440144788712</v>
       </c>
       <c r="G12" t="n">
-        <v>24.8150209505508</v>
+        <v>28.04327944912551</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68135033881794</v>
+        <v>35.8346330811921</v>
       </c>
       <c r="I12" t="n">
-        <v>2.763278147731841</v>
+        <v>2.052366975631002</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71213999168722</v>
+        <v>4.674650090492946</v>
       </c>
       <c r="K12" t="n">
-        <v>20.64626555684159</v>
+        <v>16.12319345946015</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10789204800982</v>
+        <v>42.52696398473388</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90799751962062</v>
+        <v>99.93164352090514</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.93805494741949</v>
+        <v>84.91819541781965</v>
       </c>
       <c r="C13" t="n">
-        <v>35.16507510081192</v>
+        <v>42.18238156901823</v>
       </c>
       <c r="D13" t="n">
-        <v>1.499117106476448</v>
+        <v>1.744136771493241</v>
       </c>
       <c r="E13" t="n">
-        <v>9.753120724697318</v>
+        <v>11.38040523360429</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546953251283277</v>
+        <v>0.748498519876968</v>
       </c>
       <c r="G13" t="n">
-        <v>23.19325963453597</v>
+        <v>28.34061391718906</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71598495590307</v>
+        <v>36.13774384743282</v>
       </c>
       <c r="I13" t="n">
-        <v>2.30503141862632</v>
+        <v>1.888681378992214</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716845782052047</v>
+        <v>4.678115749231051</v>
       </c>
       <c r="K13" t="n">
-        <v>23.06194505258051</v>
+        <v>15.08180458218035</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69622212028169</v>
+        <v>42.67290444216215</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92324227367412</v>
+        <v>99.93709059336074</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.51980380536753</v>
+        <v>82.85976500632535</v>
       </c>
       <c r="C14" t="n">
-        <v>39.3231150620207</v>
+        <v>40.41754088886263</v>
       </c>
       <c r="D14" t="n">
-        <v>1.500821004907424</v>
+        <v>1.658603772096361</v>
       </c>
       <c r="E14" t="n">
-        <v>12.06533212023757</v>
+        <v>11.08478974046447</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555531128053515</v>
+        <v>0.7489727383968824</v>
       </c>
       <c r="G14" t="n">
-        <v>25.04610352721651</v>
+        <v>26.95078156418455</v>
       </c>
       <c r="H14" t="n">
-        <v>36.58192559300125</v>
+        <v>36.16063926665581</v>
       </c>
       <c r="I14" t="n">
-        <v>2.847861492165997</v>
+        <v>1.574898309546773</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722206955033446</v>
+        <v>4.681079614980516</v>
       </c>
       <c r="K14" t="n">
-        <v>16.48019619463246</v>
+        <v>17.14023499367464</v>
       </c>
       <c r="L14" t="n">
-        <v>44.10186780054681</v>
+        <v>42.38976074582406</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90517905719997</v>
+        <v>99.94753662836133</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.70575824396016</v>
+        <v>81.88201301523483</v>
       </c>
       <c r="C15" t="n">
-        <v>38.94710467975069</v>
+        <v>39.65407794878141</v>
       </c>
       <c r="D15" t="n">
-        <v>1.470330148533377</v>
+        <v>1.617173659586578</v>
       </c>
       <c r="E15" t="n">
-        <v>12.21832436318965</v>
+        <v>11.03160921102147</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562764840010037</v>
+        <v>0.7493819839869935</v>
       </c>
       <c r="G15" t="n">
-        <v>24.53946188150993</v>
+        <v>26.27758044694636</v>
       </c>
       <c r="H15" t="n">
-        <v>36.61914729816291</v>
+        <v>36.18039777240217</v>
       </c>
       <c r="I15" t="n">
-        <v>2.37549004355702</v>
+        <v>1.342232541372548</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726728025006271</v>
+        <v>4.683637399918711</v>
       </c>
       <c r="K15" t="n">
-        <v>17.29424175603983</v>
+        <v>18.11798698476516</v>
       </c>
       <c r="L15" t="n">
-        <v>43.67954630053819</v>
+        <v>42.18321841533029</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92089273632872</v>
+        <v>99.95528334887686</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.18164562643344</v>
+        <v>79.38694049479973</v>
       </c>
       <c r="C16" t="n">
-        <v>36.79020943242349</v>
+        <v>37.36709396740805</v>
       </c>
       <c r="D16" t="n">
-        <v>1.374378757850498</v>
+        <v>1.514228449014269</v>
       </c>
       <c r="E16" t="n">
-        <v>11.75117699652751</v>
+        <v>10.51587347597258</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568993776409221</v>
+        <v>0.7497340981234293</v>
       </c>
       <c r="G16" t="n">
-        <v>22.93805590035051</v>
+        <v>24.60481572164577</v>
       </c>
       <c r="H16" t="n">
-        <v>36.6493080058324</v>
+        <v>36.19739795360449</v>
       </c>
       <c r="I16" t="n">
-        <v>1.98120547797584</v>
+        <v>1.119052683167756</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730621110255761</v>
+        <v>4.685838113271434</v>
       </c>
       <c r="K16" t="n">
-        <v>19.81835437356656</v>
+        <v>20.61305950520027</v>
       </c>
       <c r="L16" t="n">
-        <v>43.32545035946671</v>
+        <v>41.98256229013134</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93401416545674</v>
+        <v>99.96271576273965</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.88209155505116</v>
+        <v>84.08812773387896</v>
       </c>
       <c r="C17" t="n">
-        <v>38.03976141343946</v>
+        <v>40.50831655394946</v>
       </c>
       <c r="D17" t="n">
-        <v>1.375470802678139</v>
+        <v>1.514945772326981</v>
       </c>
       <c r="E17" t="n">
-        <v>12.53327708536665</v>
+        <v>12.18301334323156</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575007897667105</v>
+        <v>0.7500892636516354</v>
       </c>
       <c r="G17" t="n">
-        <v>23.40373811888491</v>
+        <v>26.07945785502945</v>
       </c>
       <c r="H17" t="n">
-        <v>37.12588482082119</v>
+        <v>37.67753174810107</v>
       </c>
       <c r="I17" t="n">
-        <v>1.951840001491632</v>
+        <v>1.195031853715542</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734379936041939</v>
+        <v>4.688057897822723</v>
       </c>
       <c r="K17" t="n">
-        <v>18.11790844494882</v>
+        <v>15.91187226612103</v>
       </c>
       <c r="L17" t="n">
-        <v>43.77732046319105</v>
+        <v>43.53999564629945</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93499032157933</v>
+        <v>99.96018446636992</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.43463379827206</v>
+        <v>85.56782769119681</v>
       </c>
       <c r="C18" t="n">
-        <v>35.89361792901333</v>
+        <v>41.20082773211272</v>
       </c>
       <c r="D18" t="n">
-        <v>1.286126654510562</v>
+        <v>1.51608967433592</v>
       </c>
       <c r="E18" t="n">
-        <v>11.99044808921429</v>
+        <v>12.7491163589659</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580181719067446</v>
+        <v>0.7506556394462335</v>
       </c>
       <c r="G18" t="n">
-        <v>21.8835407856536</v>
+        <v>26.21607589212146</v>
       </c>
       <c r="H18" t="n">
-        <v>37.15124224618463</v>
+        <v>37.70598121807274</v>
       </c>
       <c r="I18" t="n">
-        <v>1.627644276385066</v>
+        <v>1.938311161715585</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737613574417152</v>
+        <v>4.691597746538961</v>
       </c>
       <c r="K18" t="n">
-        <v>20.56536620172795</v>
+        <v>14.43217230880319</v>
       </c>
       <c r="L18" t="n">
-        <v>43.48679809143949</v>
+        <v>44.30243833607891</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94578222218078</v>
+        <v>99.93543837699482</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.44357912578899</v>
+        <v>82.7210931431005</v>
       </c>
       <c r="C19" t="n">
-        <v>35.14713843747492</v>
+        <v>38.65441290034482</v>
       </c>
       <c r="D19" t="n">
-        <v>1.250343502908557</v>
+        <v>1.410392852253812</v>
       </c>
       <c r="E19" t="n">
-        <v>11.88400615357357</v>
+        <v>12.12967481467498</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584571941956366</v>
+        <v>0.7511445486925105</v>
       </c>
       <c r="G19" t="n">
-        <v>21.27468779689436</v>
+        <v>24.38837667606134</v>
       </c>
       <c r="H19" t="n">
-        <v>37.17275917547548</v>
+        <v>37.73053948672314</v>
       </c>
       <c r="I19" t="n">
-        <v>1.362967839018645</v>
+        <v>1.616311335366529</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740357463722727</v>
+        <v>4.694653429328192</v>
       </c>
       <c r="K19" t="n">
-        <v>21.55642087421102</v>
+        <v>17.2789068568995</v>
       </c>
       <c r="L19" t="n">
-        <v>43.25103472483946</v>
+        <v>44.01283826604135</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95459403652541</v>
+        <v>99.94615802328566</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.81325122413979</v>
+        <v>79.68925988284549</v>
       </c>
       <c r="C20" t="n">
-        <v>32.72646783467553</v>
+        <v>35.87224331689522</v>
       </c>
       <c r="D20" t="n">
-        <v>1.155340535628196</v>
+        <v>1.298383761363858</v>
       </c>
       <c r="E20" t="n">
-        <v>11.17043728276897</v>
+        <v>11.39098733779019</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7588361477601819</v>
+        <v>0.7515679878317567</v>
       </c>
       <c r="G20" t="n">
-        <v>19.65820523512902</v>
+        <v>22.45152631879947</v>
       </c>
       <c r="H20" t="n">
-        <v>37.19133207543785</v>
+        <v>37.75180914406321</v>
       </c>
       <c r="I20" t="n">
-        <v>1.136374023914425</v>
+        <v>1.347685409048524</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742725923501135</v>
+        <v>4.697299923948481</v>
       </c>
       <c r="K20" t="n">
-        <v>24.18674877586021</v>
+        <v>20.3107401171545</v>
       </c>
       <c r="L20" t="n">
-        <v>43.04892317171375</v>
+        <v>43.77211902885677</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96213978224949</v>
+        <v>99.9551024629065</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.78742162393068</v>
+        <v>76.57813086051847</v>
       </c>
       <c r="C21" t="n">
-        <v>36.50147370403536</v>
+        <v>32.96851491249278</v>
       </c>
       <c r="D21" t="n">
-        <v>1.156070878627953</v>
+        <v>1.184012765784355</v>
       </c>
       <c r="E21" t="n">
-        <v>13.18726770001094</v>
+        <v>10.57485718678182</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7593158424055167</v>
+        <v>0.7519355763156278</v>
       </c>
       <c r="G21" t="n">
-        <v>21.42189351520082</v>
+        <v>20.47383413427675</v>
       </c>
       <c r="H21" t="n">
-        <v>38.96610383787418</v>
+        <v>37.77027338217783</v>
       </c>
       <c r="I21" t="n">
-        <v>1.551045834776785</v>
+        <v>1.123620463209416</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745724015034478</v>
+        <v>4.699597351972676</v>
       </c>
       <c r="K21" t="n">
-        <v>18.21257837606935</v>
+        <v>23.42186913948152</v>
       </c>
       <c r="L21" t="n">
-        <v>45.23427905429591</v>
+        <v>43.57218024221879</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94833113440062</v>
+        <v>99.96256429419309</v>
       </c>
     </row>
   </sheetData>
